--- a/good_comment/db/new_df.xlsx
+++ b/good_comment/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,40 +461,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3297775764767115888</t>
+          <t>3301731590618029595</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-23 13:37:55</t>
+          <t>2026-05-15 13:37:19</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具（含公道杯）*1加赠 庄园锯朵仔7g*1加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5111081066656003533</t>
+          <t>5116036356671005843</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-23 12:49:35</t>
+          <t>2026-05-15 13:30:22</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -503,60 +499,52 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5111273016030019324</t>
+          <t>3301688174944032268</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-23 12:47:02</t>
+          <t>2026-05-15 13:30:12</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3297183962088001079</t>
+          <t>5116156453717008239</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-23 12:42:15</t>
+          <t>2026-05-15 13:09:08</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>岽顶蜜兰香</t>
@@ -565,68 +553,68 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5111358193604059008</t>
+          <t>3301731446506006887</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-23 12:39:11</t>
+          <t>2026-05-15 13:08:54</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>四大老丛</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3297779112381024091</t>
+          <t>3301688390980005975</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-23 12:36:26</t>
+          <t>2026-05-15 12:54:30</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5110901103499095033</t>
+          <t>5115634347093004925</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-23 12:27:21</t>
+          <t>2026-05-15 11:59:45</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -634,27 +622,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>四大老丛</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3297151635604037059</t>
+          <t>5116034520573009821</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-23 12:20:34</t>
+          <t>2026-05-15 10:55:05</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -663,7 +651,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>金香鸭屎+庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
@@ -673,12 +661,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3297763416586017756</t>
+          <t>5116118185717015349</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-23 12:18:06</t>
+          <t>2026-05-15 10:53:03</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -686,12 +674,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>加赠老丛私房八仙7g*1</t>
+          <t>加赠清香桂花7g*1加赠岽顶蜜兰香7g*1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
@@ -701,12 +689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3297621001404009470</t>
+          <t>3302129353763006878</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-23 11:27:59</t>
+          <t>2026-05-15 10:29:57</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -715,118 +703,136 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>2.0高阶版</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5111070050624076634</t>
+          <t>5115820790817010938</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-23 11:20:24</t>
+          <t>2026-05-15 09:45:25</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1 
+加赠浓香芝兰7g*1 
+加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3297759888236044459</t>
+          <t>3302281344432008560</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-23 11:05:53</t>
+          <t>2026-05-15 09:39:48</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5111067926075068027</t>
+          <t>3302114773890017161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-23 10:41:47</t>
+          <t>2026-05-15 09:25:13</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3297137523297135890</t>
+          <t>3302288112295000089</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-23 10:34:37</t>
+          <t>2026-05-15 08:58:51</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5111340301301015042</t>
+          <t>5115628155569003737</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-23 10:07:34</t>
+          <t>2026-05-15 08:35:36</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -835,46 +841,46 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3297750240028009870</t>
+          <t>5116112353729014128</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-23 09:44:40</t>
+          <t>2026-05-15 08:20:29</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5111248032591078506</t>
+          <t>5115628443573016724</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-23 09:31:31</t>
+          <t>2026-05-15 08:03:26</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -883,22 +889,22 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5110873959801003310</t>
+          <t>5115629991202243122</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-23 09:15:26</t>
+          <t>2026-05-15 07:36:00</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -907,22 +913,22 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3297743004029036759</t>
+          <t>5115627903686007222</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-23 08:57:34</t>
+          <t>2026-05-15 07:20:16</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -931,22 +937,22 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>九大香型</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5110873239128063103</t>
+          <t>3302116141410012087</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-23 08:45:05</t>
+          <t>2026-05-15 07:07:17</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -955,78 +961,70 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5110873239128008729</t>
+          <t>5115825254583001315</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-23 08:45:05</t>
+          <t>2026-05-15 06:23:58</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5111041574957279923</t>
+          <t>5115624951363047528</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-23 08:39:26</t>
+          <t>2026-05-15 05:35:33</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3297743040053006488</t>
+          <t>5116034016568009036</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-23 07:33:55</t>
+          <t>2026-05-15 04:05:49</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1041,16 +1039,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5111238276445078436</t>
+          <t>5116120129407026023</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-23 07:09:50</t>
+          <t>2026-05-15 03:09:16</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1059,22 +1057,22 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5111239212112027549</t>
+          <t>5115822806594054508</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-23 07:03:29</t>
+          <t>2026-05-15 02:05:49</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1083,22 +1081,22 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3297736848476033754</t>
+          <t>3302282964115010798</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-23 03:29:59</t>
+          <t>2026-05-15 01:05:46</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1107,22 +1105,22 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5111233632774004041</t>
+          <t>3302114593183003094</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-23 02:53:58</t>
+          <t>2026-05-15 01:00:51</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1131,22 +1129,22 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5111040134758182048</t>
+          <t>5115629739369006944</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-23 02:09:33</t>
+          <t>2026-05-15 00:20:58</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1155,94 +1153,106 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5111319853604052406</t>
+          <t>5116027428031028432</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-23 02:08:52</t>
+          <t>2026-05-14 23:46:29</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3297738144438027784</t>
+          <t>5115622755199031528</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-23 01:54:16</t>
+          <t>2026-05-14 23:03:39</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>加赠 浓香芝兰7g*2</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3297117075631176485</t>
+          <t>5115629415219010600</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-23 01:06:10</t>
+          <t>2026-05-14 22:56:24</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5110862655910016712</t>
+          <t>3301647674001128598</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-23 00:43:46</t>
+          <t>2026-05-14 22:37:14</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1251,46 +1261,50 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3297593749628003971</t>
+          <t>3302094577494013778</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-23 00:41:14</t>
+          <t>2026-05-14 22:18:26</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5110858767008130119</t>
+          <t>3301615779001048293</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-23 00:37:20</t>
+          <t>2026-05-14 22:12:14</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1305,16 +1319,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5111228160696010401</t>
+          <t>3301647494214111384</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-23 00:12:04</t>
+          <t>2026-05-14 22:03:51</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1329,72 +1343,64 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3297730944189018075</t>
+          <t>5116030704001005435</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-23 00:11:45</t>
+          <t>2026-05-14 21:30:05</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>九大香型</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3297730080656052891</t>
+          <t>5115989808001012418</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-23 00:05:52</t>
+          <t>2026-05-14 21:27:04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5110856823626038802</t>
+          <t>3302220108001003568</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-23 00:03:24</t>
+          <t>2026-05-14 21:02:17</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1409,16 +1415,16 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3297579853350021469</t>
+          <t>5116003776001034029</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-23 00:03:02</t>
+          <t>2026-05-14 20:41:31</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1427,50 +1433,46 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5111227260372009832</t>
+          <t>3301595726345137684</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-22 23:34:18</t>
+          <t>2026-05-14 20:29:40</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠金香鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>九大香型</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5111020262154154933</t>
+          <t>5115572859618007616</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-22 22:43:59</t>
+          <t>2026-05-14 20:26:00</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1479,32 +1481,28 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3297132806673018079</t>
+          <t>5116010688001007612</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-22 21:49:03</t>
+          <t>2026-05-14 20:22:45</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
@@ -1513,46 +1511,56 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3297130538491030399</t>
+          <t>3302056885433015388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-22 21:25:09</t>
+          <t>2026-05-14 20:14:03</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>取茶三件套*1 不需要发货
+加赠 六大组合品鉴装7g*6 
+加赠 岽顶蜜兰香7g*1 庄园锯朵仔7g*1 庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3297091983100052482</t>
+          <t>3302211504035013253</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-22 20:35:17</t>
+          <t>2026-05-14 18:59:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1561,22 +1569,26 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5111281369218007815</t>
+          <t>3302048677098059487</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-22 20:07:00</t>
+          <t>2026-05-14 18:55:00</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>岽顶蜜兰香</t>
@@ -1585,149 +1597,144 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5111196012844013643</t>
+          <t>5116060909823007612</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-22 20:03:16</t>
+          <t>2026-05-14 18:20:01</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*2</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5111269741361078016</t>
+          <t>5116014649928261332</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-22 20:00:30</t>
+          <t>2026-05-14 17:14:34</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1，老丛私房宋种7g*1，老丛私房东方红7g*1</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3297702000559001192</t>
+          <t>3301561994148000973</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-22 18:36:24</t>
+          <t>2026-05-14 17:07:57</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5110974722843028333</t>
+          <t>3301999105260013980</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-22 17:30:11</t>
+          <t>2026-05-14 16:42:31</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5111262469540028333</t>
+          <t>5115883824735026015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-04-22 17:24:57</t>
+          <t>2026-05-14 16:08:16</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>加赠 老丛私房杏仁50g*1
-加赠 岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5111237053101031733</t>
+          <t>3302133780351026590</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-04-22 15:22:58</t>
+          <t>2026-05-14 15:52:17</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1742,96 +1749,107 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3297095726927019886</t>
+          <t>3301471418244101372</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-04-22 15:18:00</t>
+          <t>2026-05-14 15:38:29</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>按照备注发货，实际发货：
+老丛私房鸭屎200g*2
+老丛私房蜜兰200g*1
+老丛私房鸭屎7g*1
+老丛私房八仙7g*1
+老丛私房蜜兰7g*1
+老丛私房杏仁50g*1
+羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>补差价链接：补拍金额=支付件数</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5111140536342006208</t>
+          <t>5115486747658004119</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-04-22 14:49:54</t>
+          <t>2026-05-14 15:33:02</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>浓香芝兰</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5111113212215072202</t>
+          <t>5115873096795032035</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-04-22 13:20:08</t>
+          <t>2026-05-14 15:04:26</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3297644904590018397</t>
+          <t>5115470475481000410</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-04-22 13:18:22</t>
+          <t>2026-05-14 14:38:59</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -1842,16 +1860,16 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5110699575303011649</t>
+          <t>5115836484169006828</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-04-22 12:39:08</t>
+          <t>2026-05-14 14:17:48</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1859,27 +1877,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>待 发货</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3296987187603020699</t>
+          <t>3302043744428116484</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-04-22 12:29:58</t>
+          <t>2026-05-14 13:29:34</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1888,32 +1906,28 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5110830470379181847</t>
+          <t>3301417058831019769</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-04-22 10:39:28</t>
+          <t>2026-05-14 13:29:11</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1922,68 +1936,68 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5111111809947007412</t>
+          <t>3302049612191003378</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-04-22 09:07:08</t>
+          <t>2026-05-14 13:22:08</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5110823342526007506</t>
+          <t>5115825504789101340</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-04-22 09:03:52</t>
+          <t>2026-05-14 13:17:50</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">加赠 庄园锯朵仔7g*1 </t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3297567288830061495</t>
+          <t>5115911653171030731</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-04-22 09:03:25</t>
+          <t>2026-05-14 13:12:55</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1991,27 +2005,27 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7g*1</t>
+          <t>加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房姜花香</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5111109181371016724</t>
+          <t>3301860829321034775</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-04-22 08:42:54</t>
+          <t>2026-05-14 12:18:05</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2020,83 +2034,1914 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5110808978975055227</t>
+          <t>5115827952352025434</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-04-22 07:39:40</t>
+          <t>2026-05-14 11:49:05</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5111102341640009929</t>
+          <t>3301393155227000254</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-04-22 02:40:58</t>
+          <t>2026-05-14 11:46:54</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5111099965890005932</t>
+          <t>3301868209402023277</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-04-22 00:11:44</t>
+          <t>2026-05-14 11:38:19</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5115827880437019933</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-05-14 11:24:51</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5115418779547012116</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-05-14 11:19:12</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5115422163158012919</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:47:14</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5115614654984008206</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:46:44</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1加赠岽顶蜜兰香7g*1加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>3301395854206157573</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:31:07</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5115909457349041913</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:26:22</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3301393622340034154</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:46:54</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5115822696299015723</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:26:43</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>3301388078116152568</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:47:29</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5115903373894011017</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:38:44</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5115418779105006937</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-05-14 07:53:31</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5115901321777021228</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-05-14 06:47:21</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>浓香芝兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3301349019779002350</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-05-14 03:58:48</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>老丛私房八仙</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5115411723609009444</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-05-14 01:26:55</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>浓香芝兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3301378430257004965</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:52:18</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5115610406276002222</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:39:10</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3301364174287186572</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:27:21</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3301983552943064480</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:04:54</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5115804768549047001</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-05-13 22:33:57</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5115581858431060043</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:59:29</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5115899161065007922</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:41:14</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5115399879269080417</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:37:02</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>取茶三件套不发
+加赠庄园锯朵仔7g*1 
+加赠六大组合品鉴装7g*6</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5115869425983007219</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:21:09</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3301956228037053894</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:11:08</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5115597194764027418</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:10:31</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3301815181604010390</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:06:51</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3301978800224006351</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-05-13 21:06:22</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5115872485514049906</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-05-13 20:32:45</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5115794292064005007</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-05-13 20:04:12</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1 加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3301341386881008195</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:54:18</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>浓香芝兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3301312911279001586</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:40:29</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3301786237398033975</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:28:36</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3301284939091012585</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-05-13 17:57:53</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5115366111699007024</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-05-13 17:29:20</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3301307186053023290</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-05-13 17:10:21</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5115768012211014342</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:57:35</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>297</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5115344295913297405</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:32:30</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5115836701011000500</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:24:33</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>按备注发货 实际发：
+庄园鸭屎50g*2
+庄园鸭屎7g*4
+庄园锯朵仔7g*2</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5115715812622020015</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:23:27</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>100</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5115841273473011938</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:16:10</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*3
+庄园东方红7g*1
+庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5115512774962018929</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:02:29</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5115730968671004704</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-05-13 15:44:59</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>315</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5115504602917020431</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-05-13 15:25:40</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>317</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3301696381506030884</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-05-13 15:22:25</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3301210563474025586</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:53:43</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>323</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3301633813584061791</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:14:45</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>329</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5115675564011028647</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:06:11</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1加赠岽顶蜜兰香7g*1加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3301828320810046190</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:05:31</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>338</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5115785005120336913</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:58:04</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>老丛私房八仙</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5115459062771123146</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:29:24</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>342</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5115760885248017948</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:09:51</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>344</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3301185903220010866</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:01:35</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>345</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>3301153323495066689</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:58:25</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>347</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5115464786314004112</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:23:15</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>349</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5115465326243191425</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:18:39</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>十年陈窖藏鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>352</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5115663612966008047</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:09:16</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>总净含量:500g;口味:炭烧口味</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>355</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5115258579942006834</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:05:09</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>358</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3301630105251002889</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:58:22</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>361</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>3301616749858019898</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:51:12</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>364</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5115749725873127444</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:49:06</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>367</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5115663612900019741</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:23:58</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>369</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3301141551518008372</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:23:09</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>371</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3301166930783009789</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:04:17</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>374</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5115669840690079336</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:53:40</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5115756277255004531</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:04:20</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3301155842128001879</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-05-13 01:22:48</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>100</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>3301589029540042674</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-05-13 01:16:11</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5115260883240055536</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-05-13 01:10:08</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>393</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5115253323536001732</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:55:48</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>396</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5115450170450283229</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:16:56</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>

--- a/good_comment/db/new_df.xlsx
+++ b/good_comment/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3301731590618029595</t>
+          <t>5116635147171267917</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-15 13:37:19</t>
+          <t>2026-05-22 13:33:28</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,46 +475,50 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5116036356671005843</t>
+          <t>5117176909654013244</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-15 13:30:22</t>
+          <t>2026-05-22 13:22:10</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3301688174944032268</t>
+          <t>5116644543116008943</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-15 13:30:12</t>
+          <t>2026-05-22 12:53:28</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -523,22 +527,22 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5116156453717008239</t>
+          <t>3303134906522305773</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-15 13:09:08</t>
+          <t>2026-05-22 12:34:14</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -553,68 +557,68 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3301731446506006887</t>
+          <t>3303120003649014651</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-15 13:08:54</t>
+          <t>2026-05-22 12:06:06</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3301688390980005975</t>
+          <t>5116841678557024843</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-15 12:54:30</t>
+          <t>2026-05-22 11:58:32</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5115634347093004925</t>
+          <t>3303767496268012379</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-15 11:59:45</t>
+          <t>2026-05-22 11:16:15</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -622,79 +626,79 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5116034520573009821</t>
+          <t>3303764436954019394</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-15 10:55:05</t>
+          <t>2026-05-22 11:00:43</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>十年陈窖藏鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5116118185717015349</t>
+          <t>5116617075526026048</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-15 10:53:03</t>
+          <t>2026-05-22 10:42:46</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1加赠岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3302129353763006878</t>
+          <t>5117101237661003345</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-05-15 10:29:57</t>
+          <t>2026-05-22 10:07:55</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -703,136 +707,118 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.0高阶版</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5115820790817010938</t>
+          <t>3303058839508107091</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05-15 09:45:25</t>
+          <t>2026-05-22 09:53:16</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1 
-加赠浓香芝兰7g*1 
-加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3302281344432008560</t>
+          <t>3303093614046060177</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-15 09:39:48</t>
+          <t>2026-05-22 09:25:35</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3302114773890017161</t>
+          <t>3303539041644072666</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-15 09:25:13</t>
+          <t>2026-05-22 09:21:16</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3302288112295000089</t>
+          <t>5116809098448024924</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-05-15 08:58:51</t>
+          <t>2026-05-22 09:04:16</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5115628155569003737</t>
+          <t>5117015124312009124</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-15 08:35:36</t>
+          <t>2026-05-22 03:36:43</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -841,26 +827,26 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5116112353729014128</t>
+          <t>5117089285356022731</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-15 08:20:29</t>
+          <t>2026-05-22 01:24:37</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -871,88 +857,100 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5115628443573016724</t>
+          <t>3303061107507017590</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05-15 08:03:26</t>
+          <t>2026-05-22 00:50:06</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5115629991202243122</t>
+          <t>5116808090493002216</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-05-15 07:36:00</t>
+          <t>2026-05-22 00:46:20</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5115627903686007222</t>
+          <t>3303089942283009679</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05-15 07:20:16</t>
+          <t>2026-05-22 00:41:29</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3302116141410012087</t>
+          <t>5116596339855058545</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-05-15 07:07:17</t>
+          <t>2026-05-22 00:05:39</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -961,70 +959,78 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>老丛私房八仙</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5115825254583001315</t>
+          <t>3303083606224009380</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-15 06:23:58</t>
+          <t>2026-05-22 00:01:29</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5115624951363047528</t>
+          <t>5117009508103027434</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-15 05:35:33</t>
+          <t>2026-05-21 23:24:55</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5116034016568009036</t>
+          <t>3303712380731002098</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-15 04:05:49</t>
+          <t>2026-05-21 23:07:59</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1039,16 +1045,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5116120129407026023</t>
+          <t>3303075542500101698</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-05-15 03:09:16</t>
+          <t>2026-05-21 23:01:11</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1063,16 +1069,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5115822806594054508</t>
+          <t>5117005044698018338</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-15 02:05:49</t>
+          <t>2026-05-21 22:35:56</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1081,22 +1087,22 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3302282964115010798</t>
+          <t>5117009724048151404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-05-15 01:05:46</t>
+          <t>2026-05-21 22:28:38</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1105,22 +1111,22 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3302114593183003094</t>
+          <t>3303710580973006170</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-05-15 01:00:51</t>
+          <t>2026-05-21 22:21:29</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1129,22 +1135,22 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5115629739369006944</t>
+          <t>3303719256022006170</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-15 00:20:58</t>
+          <t>2026-05-21 22:21:00</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1153,22 +1159,22 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5116027428031028432</t>
+          <t>5116597599500064744</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-14 23:46:29</t>
+          <t>2026-05-21 22:18:32</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1176,7 +1182,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>加赠 老丛私房杏仁50g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1187,72 +1193,64 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5115622755199031528</t>
+          <t>3303710616950035892</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-14 23:03:39</t>
+          <t>2026-05-21 22:12:30</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>加赠 浓香芝兰7g*2</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5115629415219010600</t>
+          <t>3303040947747069795</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05-14 22:56:24</t>
+          <t>2026-05-21 21:46:04</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3301647674001128598</t>
+          <t>5116589823958000128</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-05-14 22:37:14</t>
+          <t>2026-05-21 21:31:12</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1261,50 +1259,46 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3302094577494013778</t>
+          <t>3303062078882011952</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-05-14 22:18:26</t>
+          <t>2026-05-21 21:24:29</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3301615779001048293</t>
+          <t>3303062510324000891</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-05-14 22:12:14</t>
+          <t>2026-05-21 21:17:43</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1319,16 +1313,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3301647494214111384</t>
+          <t>5116767158814264525</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-14 22:03:51</t>
+          <t>2026-05-21 21:13:32</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1337,22 +1331,22 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5116030704001005435</t>
+          <t>5117072725131008117</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-14 21:30:05</t>
+          <t>2026-05-21 21:13:20</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1367,40 +1361,44 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5115989808001012418</t>
+          <t>3303067550286036297</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-14 21:27:04</t>
+          <t>2026-05-21 21:03:48</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3302220108001003568</t>
+          <t>5116754666575043824</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-05-14 21:02:17</t>
+          <t>2026-05-21 21:03:12</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1409,94 +1407,106 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5116003776001034029</t>
+          <t>3303520321900002263</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-05-14 20:41:31</t>
+          <t>2026-05-21 20:57:16</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>加赠清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3301595726345137684</t>
+          <t>5116573947154006620</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-14 20:29:40</t>
+          <t>2026-05-21 20:55:50</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5115572859618007616</t>
+          <t>5116979700777001828</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-14 20:26:00</t>
+          <t>2026-05-21 20:28:46</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5116010688001007612</t>
+          <t>5116560735331000418</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-14 20:22:45</t>
+          <t>2026-05-21 20:23:02</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1505,34 +1515,28 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3302056885433015388</t>
+          <t>5116753442008012715</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-14 20:14:03</t>
+          <t>2026-05-21 20:12:02</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>取茶三件套*1 不需要发货
-加赠 六大组合品鉴装7g*6 
-加赠 岽顶蜜兰香7g*1 庄园锯朵仔7g*1 庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -1541,44 +1545,40 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3302211504035013253</t>
+          <t>3303018195992008471</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-14 18:59:00</t>
+          <t>2026-05-21 20:03:48</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3302048677098059487</t>
+          <t>5116968900910015342</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-14 18:55:00</t>
+          <t>2026-05-21 20:00:01</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1586,51 +1586,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t xml:space="preserve">取茶三件套不要发！！
+加赠庄园蜜兰7g*4
+</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5116060909823007612</t>
+          <t>3303009662974033065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-14 18:20:01</t>
+          <t>2026-05-21 19:59:31</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5116014649928261332</t>
+          <t>5116559799568151642</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-14 17:14:34</t>
+          <t>2026-05-21 19:58:12</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1645,72 +1651,64 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3301561994148000973</t>
+          <t>5116550763727023847</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-14 17:07:57</t>
+          <t>2026-05-21 19:54:21</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3301999105260013980</t>
+          <t>3303037166215211259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-14 16:42:31</t>
+          <t>2026-05-21 19:54:18</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5115883824735026015</t>
+          <t>3303037166215003451</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-14 16:08:16</t>
+          <t>2026-05-21 19:53:55</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1719,22 +1717,22 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3302133780351026590</t>
+          <t>5116749554654009912</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-14 15:52:17</t>
+          <t>2026-05-21 19:19:57</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1749,75 +1747,68 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3301471418244101372</t>
+          <t>3302989215868009765</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-14 15:38:29</t>
+          <t>2026-05-21 19:11:29</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>按照备注发货，实际发货：
-老丛私房鸭屎200g*2
-老丛私房蜜兰200g*1
-老丛私房鸭屎7g*1
-老丛私房八仙7g*1
-老丛私房蜜兰7g*1
-老丛私房杏仁50g*1
-羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>补差价链接：补拍金额=支付件数</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5115486747658004119</t>
+          <t>3303007466338025354</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-14 15:33:02</t>
+          <t>2026-05-21 19:10:57</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠金香鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5115873096795032035</t>
+          <t>5116755638358023024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-14 15:04:26</t>
+          <t>2026-05-21 19:06:55</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1825,27 +1816,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>待 发货</t>
+          <t>加赠金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5115470475481000410</t>
+          <t>5116540611510007832</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-14 14:38:59</t>
+          <t>2026-05-21 18:07:11</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1854,50 +1845,46 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5115836484169006828</t>
+          <t>5116736306361035525</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-14 14:17:48</t>
+          <t>2026-05-21 17:54:38</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3302043744428116484</t>
+          <t>3303642792760045754</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-14 13:29:34</t>
+          <t>2026-05-21 17:43:51</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1906,22 +1893,22 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3301417058831019769</t>
+          <t>5116739042415074744</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-14 13:29:11</t>
+          <t>2026-05-21 17:30:54</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1930,74 +1917,74 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3302049612191003378</t>
+          <t>3302982699354131999</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-14 13:22:08</t>
+          <t>2026-05-21 17:26:25</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5115825504789101340</t>
+          <t>3303403717770012651</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-14 13:17:50</t>
+          <t>2026-05-21 16:41:57</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5115911653171030731</t>
+          <t>5116931172911017102</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-05-14 13:12:55</t>
+          <t>2026-05-21 16:32:32</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2005,27 +1992,27 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>加赠 庄园锯朵仔7g*1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>老丛私房姜花香</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3301860829321034775</t>
+          <t>3302986982669017090</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-05-14 12:18:05</t>
+          <t>2026-05-21 15:53:56</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2034,22 +2021,22 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5115827952352025434</t>
+          <t>3303589260937000588</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05-14 11:49:05</t>
+          <t>2026-05-21 15:32:35</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2058,78 +2045,75 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3301393155227000254</t>
+          <t>3302925675462036575</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-05-14 11:46:54</t>
+          <t>2026-05-21 15:08:48</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3301868209402023277</t>
+          <t>3303574032780000253</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-05-14 11:38:19</t>
+          <t>2026-05-21 15:06:35</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>取茶三件套不要发！！！
+加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5115827880437019933</t>
+          <t>5116881312715067322</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-05-14 11:24:51</t>
+          <t>2026-05-21 14:32:41</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2137,93 +2121,81 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>待 发货</t>
+          <t>加赠清香桂花7g*1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5115418779547012116</t>
+          <t>3303568452884105695</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-14 11:19:12</t>
+          <t>2026-05-21 14:10:32</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5115422163158012919</t>
+          <t>3302909618870019698</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-05-14 10:47:14</t>
+          <t>2026-05-21 13:17:43</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5115614654984008206</t>
+          <t>5116651166855106709</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-14 10:46:44</t>
+          <t>2026-05-21 13:11:52</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1加赠岽顶蜜兰香7g*1加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2232,26 +2204,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3301395854206157573</t>
+          <t>5116863636646037022</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-05-14 10:31:07</t>
+          <t>2026-05-21 12:36:40</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2260,16 +2228,16 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5115909457349041913</t>
+          <t>5116445535066035217</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-05-14 10:26:22</t>
+          <t>2026-05-21 12:00:14</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2277,27 +2245,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>加赠清香桂花7g*1加赠 庄园锯朵仔7g*1</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3301393622340034154</t>
+          <t>5116425735653120642</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-05-14 09:46:54</t>
+          <t>2026-05-21 11:50:34</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2310,22 +2278,22 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>十年陈窖藏鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5115822696299015723</t>
+          <t>3303323833263492772</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-05-14 09:26:43</t>
+          <t>2026-05-21 11:42:46</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2340,16 +2308,16 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3301388078116152568</t>
+          <t>3303505164893067592</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-05-14 08:47:29</t>
+          <t>2026-05-21 11:09:27</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2357,51 +2325,56 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1
+礼袋需要更换为悠山蜜兰200g红色礼袋*1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5115903373894011017</t>
+          <t>3302833875395132668</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-05-14 08:38:44</t>
+          <t>2026-05-21 10:56:34</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5115418779105006937</t>
+          <t>5116935061217000510</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-05-14 07:53:31</t>
+          <t>2026-05-21 10:52:56</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2410,94 +2383,106 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5115901321777021228</t>
+          <t>3303339673882029388</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-05-14 06:47:21</t>
+          <t>2026-05-21 10:33:03</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3301349019779002350</t>
+          <t>3302835351788017971</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-05-14 03:58:48</t>
+          <t>2026-05-21 09:50:30</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>老丛私房八仙</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5115411723609009444</t>
+          <t>3302829591610098981</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-05-14 01:26:55</t>
+          <t>2026-05-21 07:20:32</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3301378430257004965</t>
+          <t>5116429263021013345</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-05-13 23:52:18</t>
+          <t>2026-05-21 06:40:21</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2512,16 +2497,16 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5115610406276002222</t>
+          <t>5116631618238043000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-05-13 23:39:10</t>
+          <t>2026-05-21 03:05:16</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2530,78 +2515,70 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3301364174287186572</t>
+          <t>3303497208367019184</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-05-13 23:27:21</t>
+          <t>2026-05-21 02:51:59</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3301983552943064480</t>
+          <t>3302811123011016199</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-05-13 23:04:54</t>
+          <t>2026-05-21 02:22:44</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5115804768549047001</t>
+          <t>3302844638309054596</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-05-13 22:33:57</t>
+          <t>2026-05-21 01:55:47</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2610,22 +2587,22 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5115581858431060043</t>
+          <t>5116919365324029139</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-05-13 21:59:29</t>
+          <t>2026-05-21 00:43:36</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2634,28 +2611,32 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5115899161065007922</t>
+          <t>3302820411662048774</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-05-13 21:41:14</t>
+          <t>2026-05-21 00:19:27</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2664,70 +2645,64 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5115399879269080417</t>
+          <t>5116901365824018308</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-13 21:37:02</t>
+          <t>2026-05-20 23:19:37</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>取茶三件套不发
-加赠庄园锯朵仔7g*1 
-加赠六大组合品鉴装7g*6</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5115869425983007219</t>
+          <t>5116394703360009307</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-05-13 21:21:09</t>
+          <t>2026-05-20 23:08:32</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3301956228037053894</t>
+          <t>5116890709073104739</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-05-13 21:11:08</t>
+          <t>2026-05-20 23:07:11</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2742,16 +2717,16 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5115597194764027418</t>
+          <t>5116883221455020239</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-05-13 21:10:31</t>
+          <t>2026-05-20 22:47:16</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2759,27 +2734,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>加赠岽顶蜜兰香7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠岽顶蜜兰香7g*1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3301815181604010390</t>
+          <t>5116374687520083001</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-05-13 21:06:51</t>
+          <t>2026-05-20 22:42:48</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2787,27 +2762,27 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+          <t>加赠清香桂花7g*1加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3301978800224006351</t>
+          <t>3303401304596032466</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-05-13 21:06:22</t>
+          <t>2026-05-20 21:08:59</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2816,84 +2791,84 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5115872485514049906</t>
+          <t>5116528766637094139</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-05-13 20:32:45</t>
+          <t>2026-05-20 19:54:25</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5115794292064005007</t>
+          <t>5116538738562104147</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-05-13 20:04:12</t>
+          <t>2026-05-20 19:43:20</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1 加赠庄园蜜兰7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3301341386881008195</t>
+          <t>3302741498629008270</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-05-13 19:54:18</t>
+          <t>2026-05-20 19:37:37</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>浓香芝兰</t>
@@ -2902,16 +2877,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3301312911279001586</t>
+          <t>3302721195217002955</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-05-13 19:40:29</t>
+          <t>2026-05-20 17:59:17</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2919,27 +2894,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3301786237398033975</t>
+          <t>5116319751827022338</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-05-13 19:28:36</t>
+          <t>2026-05-20 17:52:34</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2947,75 +2922,79 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3301284939091012585</t>
+          <t>5116734468645017744</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-13 17:57:53</t>
+          <t>2026-05-20 17:16:10</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5115366111699007024</t>
+          <t>5116737276346014539</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-13 17:29:20</t>
+          <t>2026-05-20 17:12:17</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3301307186053023290</t>
+          <t>3302733074664009798</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-13 17:10:21</t>
+          <t>2026-05-20 16:56:41</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3024,50 +3003,46 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5115768012211014342</t>
+          <t>5116322451306048012</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-05-13 16:57:35</t>
+          <t>2026-05-20 15:43:54</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5115344295913297405</t>
+          <t>5116319103666091429</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-13 16:32:30</t>
+          <t>2026-05-20 15:40:26</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3075,68 +3050,58 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>加赠庄园鸭屎7g*1</t>
+          <t>加赠 羊脂玉茶具（含公道杯）*1
+加赠 岽顶蜜兰香7g*1 浓香芝兰7g*1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5115836701011000500</t>
+          <t>3303358320398008188</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-13 16:24:33</t>
+          <t>2026-05-20 14:41:10</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>按备注发货 实际发：
-庄园鸭屎50g*2
-庄园鸭屎7g*4
-庄园锯朵仔7g*2</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5115715812622020015</t>
+          <t>3303172705398009789</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-13 16:23:27</t>
+          <t>2026-05-20 14:03:58</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>100</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
@@ -3145,16 +3110,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5115841273473011938</t>
+          <t>3303140629505021958</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-05-13 16:16:10</t>
+          <t>2026-05-20 13:52:01</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3162,29 +3127,27 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>加赠 岽顶蜜兰香7g*3
-庄园东方红7g*1
-庄园蜜兰7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房凹富后</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5115512774962018929</t>
+          <t>3302673278729050693</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-05-13 16:02:29</t>
+          <t>2026-05-20 13:23:28</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3192,27 +3155,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>待 发货</t>
+          <t>加赠金香鸭屎7g*1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5115730968671004704</t>
+          <t>3302684762660003288</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-05-13 15:44:59</t>
+          <t>2026-05-20 13:22:38</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -3221,28 +3184,33 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5115504602917020431</t>
+          <t>5116238175888100927</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-05-13 15:25:40</t>
+          <t>2026-05-20 13:11:26</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1
+加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -3251,96 +3219,92 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3301696381506030884</t>
+          <t>3303102073539160690</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-05-13 15:22:25</t>
+          <t>2026-05-20 12:45:46</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>清香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3301210563474025586</t>
+          <t>3303065713784101863</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-05-13 14:53:43</t>
+          <t>2026-05-20 12:13:51</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3301633813584061791</t>
+          <t>3302651102100018989</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-05-13 14:14:45</t>
+          <t>2026-05-20 12:05:00</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>加赠  金香鸭屎7g*1 浓香芝兰7g*1 清香鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>九大香型</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5115675564011028647</t>
+          <t>3302586843561009456</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-05-13 14:06:11</t>
+          <t>2026-05-20 10:51:31</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3348,37 +3312,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>加赠清香桂花7g*1加赠岽顶蜜兰香7g*1加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>取茶三件套*1不需要发货
+加赠 庄园锯朵仔7g*1加赠清香桂花7g*1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>总净含量:500g;口味:炭烧口味</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3301828320810046190</t>
+          <t>3303049621576008865</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-05-13 14:05:31</t>
+          <t>2026-05-20 09:56:16</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -3387,16 +3348,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5115785005120336913</t>
+          <t>5116626540909004817</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-05-13 13:58:04</t>
+          <t>2026-05-20 07:07:47</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3405,22 +3366,22 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>老丛私房八仙</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5115459062771123146</t>
+          <t>3303216948669094085</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-05-13 13:29:24</t>
+          <t>2026-05-20 01:07:57</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -3429,46 +3390,50 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5115760885248017948</t>
+          <t>3302572802741160580</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-05-13 13:09:51</t>
+          <t>2026-05-20 00:30:38</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3301185903220010866</t>
+          <t>5116707145340009444</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-05-13 13:01:35</t>
+          <t>2026-05-20 00:27:08</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3477,22 +3442,22 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3301153323495066689</t>
+          <t>5116703149362012527</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-05-13 12:58:25</t>
+          <t>2026-05-20 00:20:47</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3501,22 +3466,22 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5115464786314004112</t>
+          <t>3303200928960044165</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-05-13 11:23:15</t>
+          <t>2026-05-20 00:09:20</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3526,422 +3491,6 @@
       <c r="F120" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>349</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>5115465326243191425</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:18:39</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>十年陈窖藏鸭屎香</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>352</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>5115663612966008047</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:09:16</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>总净含量:500g;口味:炭烧口味</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>355</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>5115258579942006834</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:05:09</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>3301630105251002889</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:58:22</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>3301616749858019898</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:51:12</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>364</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>5115749725873127444</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:49:06</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>庄园锯朵仔</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>367</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>5115663612900019741</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:23:58</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>庄园蜜兰</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>369</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>3301141551518008372</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:23:09</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>371</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>3301166930783009789</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2026-05-13 10:04:17</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>待 发货</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>374</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>5115669840690079336</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-05-13 09:53:40</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>376</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>5115756277255004531</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-05-13 09:04:20</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>380</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>3301155842128001879</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-05-13 01:22:48</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>100</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>388</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>3301589029540042674</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-05-13 01:16:11</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>390</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>5115260883240055536</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-05-13 01:10:08</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>庄园鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>393</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>5115253323536001732</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-05-13 00:55:48</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>金香鸭屎</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>396</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>5115450170450283229</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-05-13 00:16:56</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>

--- a/good_comment/db/new_df.xlsx
+++ b/good_comment/db/new_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,36 +461,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5116635147171267917</t>
+          <t>3309188844058383065</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-22 13:33:28</t>
+          <t>2026-06-18 13:47:26</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5117176909654013244</t>
+          <t>3309193524105037991</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-22 13:22:10</t>
+          <t>2026-06-18 13:40:24</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -498,12 +502,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园鸭屎7g*1</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
@@ -513,12 +517,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5116644543116008943</t>
+          <t>3308481699309021592</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-22 12:53:28</t>
+          <t>2026-06-18 12:31:12</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -527,7 +531,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
@@ -537,36 +541,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3303134906522305773</t>
+          <t>3308966509441013890</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-22 12:34:14</t>
+          <t>2026-06-18 12:18:02</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3303120003649014651</t>
+          <t>3308453943646001774</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-22 12:06:06</t>
+          <t>2026-06-18 12:13:21</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -574,27 +582,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5116841678557024843</t>
+          <t>5120264127411022014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-22 11:58:32</t>
+          <t>2026-06-18 11:58:05</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -603,150 +611,154 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3303767496268012379</t>
+          <t>5120690832598024838</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-22 11:16:15</t>
+          <t>2026-06-18 11:56:22</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>九大香型</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3303764436954019394</t>
+          <t>5120768017542016448</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-22 11:00:43</t>
+          <t>2026-06-18 11:51:26</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>十年陈窖藏鸭屎香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5116617075526026048</t>
+          <t>5120260887813014719</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:42:46</t>
+          <t>2026-06-18 11:49:55</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5117101237661003345</t>
+          <t>5120748361754005925</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:07:55</t>
+          <t>2026-06-18 11:47:30</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*2，浓香芝兰7g*2</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3303058839508107091</t>
+          <t>3308474498045047061</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05-22 09:53:16</t>
+          <t>2026-06-18 11:24:16</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>老丛私房八仙</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3303093614046060177</t>
+          <t>5120258511307005708</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-22 09:25:35</t>
+          <t>2026-06-18 11:16:33</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -755,22 +767,22 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3303539041644072666</t>
+          <t>3308444367750035472</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-22 09:21:16</t>
+          <t>2026-06-18 11:12:20</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -779,46 +791,50 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>老丛私房鸭屎香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5116809098448024924</t>
+          <t>5120666172286003025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-05-22 09:04:16</t>
+          <t>2026-06-18 11:08:03</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5117015124312009124</t>
+          <t>3309090096373022879</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-22 03:36:43</t>
+          <t>2026-06-18 11:07:12</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -827,84 +843,80 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5117089285356022731</t>
+          <t>5120663328577121734</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-22 01:24:37</t>
+          <t>2026-06-18 11:06:56</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3303061107507017590</t>
+          <t>3308444223730005871</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05-22 00:50:06</t>
+          <t>2026-06-18 11:04:00</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5116808090493002216</t>
+          <t>3308472086419109291</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-05-22 00:46:20</t>
+          <t>2026-06-18 11:03:53</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -913,44 +925,40 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3303089942283009679</t>
+          <t>5120667720006032536</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05-22 00:41:29</t>
+          <t>2026-06-18 11:00:18</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5116596339855058545</t>
+          <t>5120439374828003705</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-05-22 00:05:39</t>
+          <t>2026-06-18 11:00:18</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -959,78 +967,70 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>老丛私房八仙</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3303083606224009380</t>
+          <t>5120237523222002201</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-22 00:01:29</t>
+          <t>2026-06-18 10:56:05</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5117009508103027434</t>
+          <t>3308904589989008776</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-21 23:24:55</t>
+          <t>2026-06-18 10:54:24</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3303712380731002098</t>
+          <t>3308456390514045673</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-21 23:07:59</t>
+          <t>2026-06-18 10:38:00</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1039,7 +1039,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
@@ -1049,21 +1049,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3303075542500101698</t>
+          <t>5120440310575014944</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-05-21 23:01:11</t>
+          <t>2026-06-18 10:37:03</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1077,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5117005044698018338</t>
+          <t>5120739397887013145</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-21 22:35:56</t>
+          <t>2026-06-18 10:30:55</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1087,22 +1091,22 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5117009724048151404</t>
+          <t>3308451242868064775</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-05-21 22:28:38</t>
+          <t>2026-06-18 10:18:46</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1111,7 +1115,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1125,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3303710580973006170</t>
+          <t>5120663904492054227</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-05-21 22:21:29</t>
+          <t>2026-06-18 10:18:41</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1135,122 +1139,130 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3303719256022006170</t>
+          <t>3308903833681057786</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-21 22:21:00</t>
+          <t>2026-06-18 10:13:23</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5116597599500064744</t>
+          <t>5120745121021027843</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-21 22:18:32</t>
+          <t>2026-06-18 10:00:22</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3303710616950035892</t>
+          <t>5120233779257029538</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-21 22:12:30</t>
+          <t>2026-06-18 09:58:30</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>四大老丛</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3303040947747069795</t>
+          <t>5120658828978018731</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05-21 21:46:04</t>
+          <t>2026-06-18 09:46:11</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5116589823958000128</t>
+          <t>5120743789006022521</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-05-21 21:31:12</t>
+          <t>2026-06-18 09:42:29</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1259,22 +1271,22 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3303062078882011952</t>
+          <t>3309066228964056060</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-05-21 21:24:29</t>
+          <t>2026-06-18 09:34:39</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1283,70 +1295,78 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3303062510324000891</t>
+          <t>5120740981318010832</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-05-21 21:17:43</t>
+          <t>2026-06-18 09:31:42</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5116767158814264525</t>
+          <t>3308894221136269763</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-21 21:13:32</t>
+          <t>2026-06-18 09:31:06</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5117072725131008117</t>
+          <t>5120663292271015233</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-21 21:13:20</t>
+          <t>2026-06-18 09:28:00</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1361,124 +1381,116 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3303067550286036297</t>
+          <t>5120738137807182019</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03:48</t>
+          <t>2026-06-18 09:17:40</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5116754666575043824</t>
+          <t>3309069792496003666</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-05-21 21:03:12</t>
+          <t>2026-06-18 09:05:55</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3303520321900002263</t>
+          <t>3308448542696015153</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-05-21 20:57:16</t>
+          <t>2026-06-18 07:47:50</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5116573947154006620</t>
+          <t>3308893177859017186</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-21 20:55:50</t>
+          <t>2026-06-18 07:40:06</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>加赠庄园鸭屎7g*1</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5116979700777001828</t>
+          <t>3308423631961070081</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-21 20:28:46</t>
+          <t>2026-06-18 07:29:11</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1486,27 +1498,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>加赠庄园蜜兰7g*1</t>
+          <t>加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>十年陈窖藏鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5116560735331000418</t>
+          <t>3308455238285030667</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-21 20:23:02</t>
+          <t>2026-06-18 07:21:31</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1515,46 +1527,50 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5116753442008012715</t>
+          <t>3308453186326047658</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-21 20:12:02</t>
+          <t>2026-06-18 07:20:26</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3303018195992008471</t>
+          <t>3308896453095021485</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-21 20:03:48</t>
+          <t>2026-06-18 07:08:48</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1569,98 +1585,93 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5116968900910015342</t>
+          <t>5120439518236014836</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-21 20:00:01</t>
+          <t>2026-06-18 07:02:52</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">取茶三件套不要发！！
-加赠庄园蜜兰7g*4
-</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3303009662974033065</t>
+          <t>3309072240270014386</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-21 19:59:31</t>
+          <t>2026-06-18 06:28:50</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房鸭屎香</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5116559799568151642</t>
+          <t>3308446094914009856</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-21 19:58:12</t>
+          <t>2026-06-18 04:17:52</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>取茶三件套*1 不需要发货
+加赠 岽顶蜜兰香7g*1 庄园鸭屎7g*1 清香桂花7g*1</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>总净含量:500g;口味:炭烧口味</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5116550763727023847</t>
+          <t>3309067056988007987</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-21 19:54:21</t>
+          <t>2026-06-18 03:33:51</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1675,16 +1686,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3303037166215211259</t>
+          <t>3308887777985000397</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-21 19:54:18</t>
+          <t>2026-06-18 02:33:06</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1693,22 +1704,22 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3303037166215003451</t>
+          <t>5120229423911024139</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-21 19:53:55</t>
+          <t>2026-06-18 02:21:57</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1717,22 +1728,22 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5116749554654009912</t>
+          <t>5120436314797028530</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-21 19:19:57</t>
+          <t>2026-06-18 01:35:24</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1747,40 +1758,44 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3302989215868009765</t>
+          <t>3308443862576076177</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-21 19:11:29</t>
+          <t>2026-06-18 01:25:52</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3303007466338025354</t>
+          <t>5120438546313019526</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-21 19:10:57</t>
+          <t>2026-06-18 00:52:24</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1788,27 +1803,28 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠金香鸭屎7g*1</t>
+          <t>取茶三件套*1 不需要发货
+加赠 岽顶蜜兰香7g*1 清香桂花7g*1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5116755638358023024</t>
+          <t>5120229423911004123</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-21 19:06:55</t>
+          <t>2026-06-18 00:50:10</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1816,27 +1832,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>加赠金香鸭屎7g*1</t>
+          <t>加赠老丛私房杏仁50g*2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>老丛私房姜花香</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5116540611510007832</t>
+          <t>3308445410770002278</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-21 18:07:11</t>
+          <t>2026-06-18 00:45:24</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1845,22 +1861,22 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5116736306361035525</t>
+          <t>3308889505280395350</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-21 17:54:38</t>
+          <t>2026-06-18 00:38:51</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1875,64 +1891,72 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3303642792760045754</t>
+          <t>5120659692671095617</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-21 17:43:51</t>
+          <t>2026-06-18 00:31:34</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5116739042415074744</t>
+          <t>5120658648858005210</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-21 17:30:54</t>
+          <t>2026-06-18 00:23:04</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3302982699354131999</t>
+          <t>5120234139108206422</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-21 17:26:25</t>
+          <t>2026-06-18 00:13:02</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1941,22 +1965,22 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3303403717770012651</t>
+          <t>5120437178668009608</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-21 16:41:57</t>
+          <t>2026-06-17 23:47:10</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1969,98 +1993,102 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5116931172911017102</t>
+          <t>3308876545953189880</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-05-21 16:32:32</t>
+          <t>2026-06-17 23:13:03</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3302986982669017090</t>
+          <t>5120227515785089309</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-05-21 15:53:56</t>
+          <t>2026-06-17 22:46:46</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3303589260937000588</t>
+          <t>5120434802854001147</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05-21 15:32:35</t>
+          <t>2026-06-17 22:28:18</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3302925675462036575</t>
+          <t>3309051756509000056</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-05-21 15:08:48</t>
+          <t>2026-06-17 22:09:54</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2069,51 +2097,46 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3303574032780000253</t>
+          <t>5120734465742032808</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-05-21 15:06:35</t>
+          <t>2026-06-17 21:57:16</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>取茶三件套不要发！！！
-加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5116881312715067322</t>
+          <t>5120230539297030027</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:41</t>
+          <t>2026-06-17 21:51:02</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2121,7 +2144,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>加赠清香桂花7g*1</t>
+          <t>加赠庄园鸭屎7g*1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2132,16 +2155,16 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3303568452884105695</t>
+          <t>3308881549595049051</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-21 14:10:32</t>
+          <t>2026-06-17 21:47:16</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2150,22 +2173,22 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>庄园东方红</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3302909618870019698</t>
+          <t>3309062052013045785</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-05-21 13:17:43</t>
+          <t>2026-06-17 21:44:58</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2180,16 +2203,16 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5116651166855106709</t>
+          <t>5120657676639043119</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-21 13:11:52</t>
+          <t>2026-06-17 21:32:23</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2198,28 +2221,32 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>九大香型</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5116863636646037022</t>
+          <t>3308879929533012950</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-05-21 12:36:40</t>
+          <t>2026-06-17 21:22:18</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2228,44 +2255,40 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5116445535066035217</t>
+          <t>5120430230182024508</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-05-21 12:00:14</t>
+          <t>2026-06-17 21:03:16</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5116425735653120642</t>
+          <t>5120657964561003219</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-05-21 11:50:34</t>
+          <t>2026-06-17 20:58:32</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2273,51 +2296,55 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>加赠老丛私房杏仁50g*1</t>
+          <t>加赠庄园蜜兰7g*1加赠清香桂花7g*1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>十年陈窖藏鸭屎香</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3303323833263492772</t>
+          <t>5120430230182053604</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-05-21 11:42:46</t>
+          <t>2026-06-17 20:44:33</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*2</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3303505164893067592</t>
+          <t>3308880289203019487</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-05-21 11:09:27</t>
+          <t>2026-06-17 20:38:48</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2325,149 +2352,140 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1
-礼袋需要更换为悠山蜜兰200g红色礼袋*1</t>
+          <t>加赠庄园蜜兰7g*1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3302833875395132668</t>
+          <t>5120656128492024321</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-05-21 10:56:34</t>
+          <t>2026-06-17 20:38:06</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房东方红</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5116935061217000510</t>
+          <t>3308426330059036281</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-05-21 10:52:56</t>
+          <t>2026-06-17 20:17:24</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>加赠六大组合品鉴装7g*12</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3303339673882029388</t>
+          <t>3308394939977010984</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-05-21 10:33:03</t>
+          <t>2026-06-17 20:15:47</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3302835351788017971</t>
+          <t>5120425334850004012</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-05-21 09:50:30</t>
+          <t>2026-06-17 19:33:21</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3302829591610098981</t>
+          <t>5120623080215086026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-05-21 07:20:32</t>
+          <t>2026-06-17 19:18:31</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具(含公道杯)*1</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
@@ -2477,36 +2495,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5116429263021013345</t>
+          <t>3308838745106021482</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-05-21 06:40:21</t>
+          <t>2026-06-17 19:15:10</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*2</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5116631618238043000</t>
+          <t>5120647488847039229</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-05-21 03:05:16</t>
+          <t>2026-06-17 18:47:00</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2515,22 +2537,22 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3303497208367019184</t>
+          <t>5120220819306007537</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-05-21 02:51:59</t>
+          <t>2026-06-17 18:22:15</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2539,22 +2561,22 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>悠山蜜兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3302811123011016199</t>
+          <t>5120195475199015538</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-05-21 02:22:44</t>
+          <t>2026-06-17 17:32:00</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2563,152 +2585,168 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3302844638309054596</t>
+          <t>3308791945419008364</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:47</t>
+          <t>2026-06-17 16:42:41</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5116919365324029139</t>
+          <t>5120591184111002535</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-05-21 00:43:36</t>
+          <t>2026-06-17 16:10:11</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3302820411662048774</t>
+          <t>3308286147937005764</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-05-21 00:19:27</t>
+          <t>2026-06-17 16:05:10</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>加赠 庄园锯朵仔7g*1</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>六大香型进阶版</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5116901365824018308</t>
+          <t>5120553888144010913</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-20 23:19:37</t>
+          <t>2026-06-17 15:48:31</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>清香桂花</t>
+          <t>庄园锯朵仔</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5116394703360009307</t>
+          <t>3308287875457038495</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-05-20 23:08:32</t>
+          <t>2026-06-17 15:45:30</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>100</v>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>加赠 庄园鸭屎7g*1</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>六大香型300g</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5116890709073104739</t>
+          <t>3308286435940059956</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-05-20 23:07:11</t>
+          <t>2026-06-17 15:41:29</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>庄园鸭屎</t>
@@ -2717,54 +2755,46 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5116883221455020239</t>
+          <t>3308278659509053373</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-05-20 22:47:16</t>
+          <t>2026-06-17 15:06:38</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>悠山蜜兰</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5116374687520083001</t>
+          <t>3308750761310014683</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-05-20 22:42:48</t>
+          <t>2026-06-17 15:03:16</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>加赠清香桂花7g*1加赠庄园蜜兰7g*1</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>金香鸭屎</t>
@@ -2773,96 +2803,92 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3303401304596032466</t>
+          <t>5120325362945093226</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-05-20 21:08:59</t>
+          <t>2026-06-17 14:44:15</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5116528766637094139</t>
+          <t>5120119911228005019</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-05-20 19:54:25</t>
+          <t>2026-06-17 14:18:33</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>加赠老丛私房杏仁50g*1</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>老丛私房宋种</t>
+          <t>清香桂花</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5116538738562104147</t>
+          <t>5120322878686018642</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-05-20 19:43:20</t>
+          <t>2026-06-17 13:50:04</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3302741498629008270</t>
+          <t>3308275059469030672</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-05-20 19:37:37</t>
+          <t>2026-06-17 13:35:33</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2871,22 +2897,22 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>浓香芝兰</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3302721195217002955</t>
+          <t>3308235674276107293</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-05-20 17:59:17</t>
+          <t>2026-06-17 13:13:10</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2894,27 +2920,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+          <t>待 发货</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5116319751827022338</t>
+          <t>5120305562357000928</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-05-20 17:52:34</t>
+          <t>2026-06-17 12:52:13</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2927,50 +2953,46 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5116734468645017744</t>
+          <t>5120092623486006142</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-20 17:16:10</t>
+          <t>2026-06-17 12:35:29</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1加赠岽顶蜜兰香7g*1</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5116737276346014539</t>
+          <t>5120571097824132308</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-20 17:12:17</t>
+          <t>2026-06-17 12:11:39</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2979,22 +3001,22 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3302733074664009798</t>
+          <t>3308251982419013790</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-20 16:56:41</t>
+          <t>2026-06-17 11:50:59</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3009,40 +3031,44 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5116322451306048012</t>
+          <t>3308848392052008471</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-05-20 15:43:54</t>
+          <t>2026-06-17 11:20:08</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5116319103666091429</t>
+          <t>3308211627542013182</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-20 15:40:26</t>
+          <t>2026-06-17 11:12:56</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3050,28 +3076,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>加赠 羊脂玉茶具（含公道杯）*1
-加赠 岽顶蜜兰香7g*1 浓香芝兰7g*1</t>
+          <t>加赠老丛私房杏仁50g*1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>老丛私房宋种</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3303358320398008188</t>
+          <t>5120477136046069533</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-20 14:41:10</t>
+          <t>2026-06-17 11:06:29</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3080,74 +3105,76 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3303172705398009789</t>
+          <t>3308219654710012899</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-20 14:03:58</t>
+          <t>2026-06-17 10:58:44</t>
         </is>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1
+加赠 庄园东方红7g*1
+加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3303140629505021958</t>
+          <t>5120252642881025530</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-05-20 13:52:01</t>
+          <t>2026-06-17 10:49:38</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>老丛私房凹富后</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3302673278729050693</t>
+          <t>5120476524057018539</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-05-20 13:23:28</t>
+          <t>2026-06-17 10:03:14</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3155,7 +3182,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>加赠金香鸭屎7g*1</t>
+          <t>待 发货</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3166,16 +3193,16 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3302684762660003288</t>
+          <t>3308831832996013697</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-05-20 13:22:38</t>
+          <t>2026-06-17 09:46:45</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -3184,51 +3211,46 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5116238175888100927</t>
+          <t>5120544961833006745</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-05-20 13:11:26</t>
+          <t>2026-06-17 09:44:29</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>加赠 岽顶蜜兰香7g*1
-加赠 羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>庄园鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3303102073539160690</t>
+          <t>5120258366394012637</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-05-20 12:45:46</t>
+          <t>2026-06-17 09:30:06</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3237,46 +3259,50 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>清香鸭屎</t>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3303065713784101863</t>
+          <t>3308208026699024285</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-05-20 12:13:51</t>
+          <t>2026-06-17 09:14:51</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>庄园蜜兰</t>
+          <t>九大香型</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3302651102100018989</t>
+          <t>3308640781255010187</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-05-20 12:05:00</t>
+          <t>2026-06-17 09:08:04</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3284,56 +3310,51 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>加赠  金香鸭屎7g*1 浓香芝兰7g*1 清香鸭屎7g*1</t>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>九大香型</t>
+          <t>庄园东方红</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3302586843561009456</t>
+          <t>5120548201595010843</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-05-20 10:51:31</t>
+          <t>2026-06-17 08:52:05</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>取茶三件套*1不需要发货
-加赠 庄园锯朵仔7g*1加赠清香桂花7g*1</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>总净含量:500g;口味:炭烧口味</t>
+          <t>六大香型300g</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3303049621576008865</t>
+          <t>5120035959638029340</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-05-20 09:56:16</t>
+          <t>2026-06-17 08:48:25</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -3348,16 +3369,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5116626540909004817</t>
+          <t>5120255450525022640</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-05-20 07:07:47</t>
+          <t>2026-06-17 08:25:31</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3366,74 +3387,74 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3303216948669094085</t>
+          <t>3308184735663009482</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-05-20 01:07:57</t>
+          <t>2026-06-17 08:12:40</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>0</v>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>六大香型进阶版</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3302572802741160580</t>
+          <t>5120471484518039642</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-05-20 00:30:38</t>
+          <t>2026-06-17 08:12:13</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>加赠羊脂玉茶具（含公道杯）*1</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>岽顶蜜兰香</t>
+          <t>庄园蜜兰</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5116707145340009444</t>
+          <t>3308644885099014997</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-05-20 00:27:08</t>
+          <t>2026-06-17 07:10:38</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3442,22 +3463,22 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>庄园锯朵仔</t>
+          <t>庄园鸭屎</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5116703149362012527</t>
+          <t>3308821968848054493</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-05-20 00:20:47</t>
+          <t>2026-06-17 06:30:28</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3466,22 +3487,22 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>金香鸭屎</t>
+          <t>岽顶蜜兰香</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3303200928960044165</t>
+          <t>3308642689080070675</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-05-20 00:09:20</t>
+          <t>2026-06-17 03:41:22</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3490,7 +3511,2186 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>346</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5120457192388014741</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:13:27</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>349</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3308822580604018895</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-06-17 01:45:04</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>清香桂花</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>353</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3308638873704012457</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:35:39</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>355</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5120250806001056303</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:14:06</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>357</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>3308194526217005795</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:03:05</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>3308820744041028955</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:51:43</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>363</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5120537005894003042</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:39:32</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>366</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5120417304914027345</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:15:09</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>369</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5120460864243049241</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:53:57</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>庄园东方红7g*1替换为岽顶蜜兰7g*1
+发顺丰！！！</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>6泡品鉴装</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5120456004281015638</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:26:46</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>372</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>3308812788024104786</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:48:48</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>375</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5120386776006349807</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:40:57</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>九大香型</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>377</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5120534989907283541</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:36:09</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5120463096001002732</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:31:19</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1 加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>383</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5120455104176019239</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:30:13</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>386</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>3308623717001116367</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:18:43</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5120460072001018133</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:18:09</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5120418744190032939</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:17:14</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>清香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5120247746001036845</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:10:33</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>100</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>398</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5120442072244017331</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-06-16 20:39:20</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1
+加赠 庄园锯朵仔7g*1
+加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3308158382935006789</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-06-16 20:33:34</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>403</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5120004423945162906</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-06-16 20:32:57</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>406</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5119964319669059119</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-06-16 20:27:13</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>409</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5120501689705009515</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-06-16 20:20:17</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5119976739582028546</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:21:38</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>3308104527588109663</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:17:45</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>加赠：老丛私房杏仁25g*1（用50g罐子包装）加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>417</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5120398080001212947</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:41:22</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>加赠庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>419</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3308729808328011895</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:39:05</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发顺丰
+加赠 咖啡色两罐装礼袋*2
+加赠 庄园锯朵仔7g*1 </t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>427</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3308725128974033756</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:06:57</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具(含公道杯)*1</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>庄园锯朵仔</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>430</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5119966299392066145</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:04:46</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>432</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5119960575660024107</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:24:49</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>434</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>3308065395307007596</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:14:30</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>437</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>3308088398384234765</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:08:18</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>439</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3308063739370021778</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:02:04</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>442</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5120457625616015700</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-06-16 15:39:07</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3308527237227008475</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-06-16 15:28:25</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>448</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>3308086922023003057</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-06-16 15:06:33</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>451</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5120164910465009037</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-06-16 15:03:23</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>加赠 羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>454</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5120456977686020035</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-06-16 15:01:59</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5120378496047077811</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-06-16 14:53:10</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>462</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5120125274965042501</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:52:38</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>老丛私房蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>464</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>3308011107135021167</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:51:00</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>467</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3308664036633022173</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:48:23</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>470</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5120452981184003527</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:33:01</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>473</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3308027019591010585</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:29:16</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>475</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3308010747623060054</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:12:46</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>加赠岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>477</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3308012187218047091</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:12:26</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>加赠 庄园锯朵仔7g*1</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5119912551678054504</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:08:32</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1加赠庄园蜜兰7g*1
+发顺丰空运</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>483</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3308638584342076264</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:59:03</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>485</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>3308009991555023493</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:22:09</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>489</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5120341164460077217</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:10:34</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>491</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5120418745646172626</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:35:42</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>493</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5120315136593014508</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:29:48</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>496</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3308464093372014387</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:28:10</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3308457937616025561</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:21:17</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>502</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5120339976534010741</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:20:32</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>505</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3308025218459004774</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:13:39</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>508</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5120336952067003516</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:33:22</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>加赠老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>十年陈窖藏鸭屎香</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>511</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3307970786117053864</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:29:54</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>按备注发货实际发：
+岽顶蜜兰50g*1
+庄园蜜兰50g*1
+庄园东方红50g*1
+庄园鸭屎50g*1
+咖啡色两罐装礼袋*2
+发顺丰</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>519</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5119908195668015011</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:29:16</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>522</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5120383069569007743</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:26:13</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>525</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5120298540949007013</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:23:00</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>527</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5119875723726009919</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:22:52</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>待 发货</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>530</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3308584872809116865</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:03:06</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>加赠庄园蜜兰7g*1</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>532</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3308409445979000099</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:01:06</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>535</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>3308403577901128098</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:45:10</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>六大香型进阶版</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>537</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5120380657247097312</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:40:52</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>541</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3308419561313004385</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:29:11</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>加赠庄园鸭屎7g*1</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>543</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5120382745477018619</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:27:44</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>加赠 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>546</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5120087402792002210</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:14:49</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>549</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5120383501400022432</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:11:32</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>551</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5119879323244002210</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:04:45</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>加赠 老丛私房杏仁50g*1</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰香</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>555</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5120297388891039742</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:57:48</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>庄园蜜兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>557</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5119877955461028722</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:49:59</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>加赠羊脂玉茶具（含公道杯）*1</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>九大香型</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>559</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>3308417653110024685</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:49:21</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>561</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5119880619016042907</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:43:02</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>563</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5120300052565009323</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:29:12</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>取茶三件套*2不需要发货 
+加赠 羊脂玉茶具（含公道杯）*1
+加赠  庄园鸭屎7g*1 庄园东方红7g*1 庄园锯朵仔7g*1 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>总净含量:500g;口味:炭烧口味</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>569</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5120384617163011410</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-06-16 08:21:34</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>六大香型300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>571</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5119879575176008447</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-06-16 07:34:35</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>取茶三件套*1 不需要发货
+加赠 六大组合品鉴装42g*1
+加赠 庄园锯朵仔7g*1 岽顶蜜兰香7g*1</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>574</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>5119867947946077419</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:54:56</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>576</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>3307963406302017297</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:38:31</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>578</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5120380585013075745</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:33:59</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>庄园鸭屎</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>3307958978595046185</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:22:57</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>发顺丰 
+按备注发货 实际发：
+庄园东方红50g*1
+庄园锯朵仔50g*1
+庄园东方红7g*1
+庄园锯朵仔7g*1 
+庄园鸭屎7g*1 
+加赠 咖啡色两罐装礼袋*1</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>庄园东方红</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>583</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>5119870179592199033</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:08:27</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>金香鸭屎</t>
         </is>
       </c>
     </row>
